--- a/data/gravel/Good Weather Olallie 2026.xlsx
+++ b/data/gravel/Good Weather Olallie 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB16122-6771-E64D-AE50-BFB9C314C27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC7F3E3-220D-1743-8385-3C6D35E2B183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -353,10 +353,7 @@
     <t>https://goodweatherinseattle.com/cdn/shop/files/vertical-DSCF2351.jpg?v=1750917738&amp;width=1200</t>
   </si>
   <si>
-    <t>Enve Adventure, not the steel fork</t>
-  </si>
-  <si>
-    <t>bikeinsights</t>
+    <t>email</t>
   </si>
 </sst>
 </file>
@@ -989,39 +986,49 @@
         <v>24</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="G18" s="4">
-        <v>398</v>
-      </c>
-      <c r="H18" s="4">
-        <v>398</v>
-      </c>
-      <c r="I18" s="4">
-        <v>398</v>
-      </c>
-      <c r="J18" s="4">
-        <v>398</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="C18" s="6">
+        <v>410</v>
+      </c>
+      <c r="D18" s="6">
+        <v>410</v>
+      </c>
+      <c r="E18" s="6">
+        <v>410</v>
+      </c>
+      <c r="F18" s="6">
+        <v>410</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>106</v>
       </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="G19" s="4">
-        <v>46</v>
-      </c>
-      <c r="H19" s="4">
-        <v>46</v>
-      </c>
-      <c r="I19" s="4">
-        <v>46</v>
-      </c>
-      <c r="J19" s="4">
-        <v>46</v>
-      </c>
+      <c r="C19" s="6">
+        <v>55</v>
+      </c>
+      <c r="D19" s="6">
+        <v>55</v>
+      </c>
+      <c r="E19" s="6">
+        <v>55</v>
+      </c>
+      <c r="F19" s="6">
+        <v>55</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11">
@@ -1052,7 +1059,7 @@
         <v>186</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:11">
